--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/may-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19357,7 +19357,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/may-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/may-2026.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dirección de Telecomunicaciones e Informática de la Armada</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Superintendencia de Insolvencia y Reemprendimiento</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>AURA XD SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Instituto Nacional de la Juventud</t>
+          <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>AURA XD SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Clínica Reproducción Humana UV</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Subsecretaria de Transportes</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCAC</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE SEGURIDAD PÚBLICA</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14647,7 +14647,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15861,7 +15861,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Dirección de Telecomunicaciones e Informática de la Armada</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -17400,12 +17400,12 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18681,7 +18681,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE REDES ASISTENCIALES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DIVISION DE SALUD</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DIVISION DE SALUD</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20206,7 +20206,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/may-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/may-2026.xlsx
@@ -562,7 +562,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1074,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1200,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1326,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1391,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1456,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1521,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1586,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1712,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1790,7 +1842,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1851,7 +1907,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1912,7 +1972,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2034,7 +2098,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2095,7 +2163,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2217,7 +2289,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2339,7 +2415,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2400,7 +2480,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2461,7 +2545,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2522,7 +2610,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2583,7 +2675,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2644,7 +2740,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2705,7 +2805,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2766,7 +2870,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2827,7 +2935,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3132,7 +3244,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3193,7 +3309,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3254,7 +3374,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3315,7 +3439,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3437,7 +3565,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3498,7 +3630,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3620,7 +3756,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3742,7 +3882,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3803,7 +3947,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3864,7 +4012,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3925,7 +4077,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3986,7 +4142,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4047,7 +4207,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4108,7 +4272,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4169,7 +4337,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4230,7 +4402,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4291,7 +4467,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4535,7 +4715,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4596,7 +4780,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4657,7 +4845,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4718,7 +4910,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4840,7 +5036,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4901,7 +5101,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4962,7 +5166,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5084,7 +5292,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5206,7 +5418,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5389,7 +5605,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5450,7 +5670,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5511,7 +5735,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5633,7 +5861,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5755,7 +5987,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5816,7 +6052,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5877,7 +6117,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5938,7 +6182,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5999,7 +6247,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6060,7 +6312,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6121,7 +6377,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6182,7 +6442,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6304,7 +6568,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6365,7 +6633,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6426,7 +6698,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6487,7 +6763,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6548,7 +6828,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6670,7 +6954,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6731,7 +7019,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6792,7 +7084,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6914,7 +7210,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7036,7 +7336,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7097,7 +7401,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7158,7 +7466,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7219,7 +7531,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7341,7 +7657,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7402,7 +7722,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7646,7 +7970,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7829,7 +8157,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7890,7 +8222,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7951,7 +8287,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8012,7 +8352,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8417,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8134,7 +8482,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8195,7 +8547,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8256,7 +8612,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8317,7 +8677,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8439,7 +8803,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8500,7 +8868,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8622,7 +8994,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8744,7 +9120,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8805,7 +9185,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8927,7 +9311,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8988,7 +9376,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9110,7 +9502,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9171,7 +9567,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9232,7 +9632,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9354,7 +9758,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9537,7 +9945,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9659,7 +10071,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9720,7 +10136,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9781,7 +10201,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9842,7 +10266,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9964,7 +10392,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10086,7 +10518,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10147,7 +10583,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10208,7 +10648,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10269,7 +10713,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10330,7 +10778,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10391,7 +10843,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10635,7 +11091,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10818,7 +11278,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11001,7 +11465,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11062,7 +11530,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11245,7 +11717,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11306,7 +11782,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11367,7 +11847,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11428,7 +11912,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11550,7 +12038,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11611,7 +12103,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11916,7 +12412,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11977,7 +12477,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12099,7 +12603,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12160,7 +12668,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12591,7 +13103,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12652,7 +13168,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12713,7 +13233,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12774,7 +13298,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12896,7 +13424,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13140,7 +13672,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13262,7 +13798,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13323,7 +13863,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13384,7 +13928,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13445,7 +13993,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13628,7 +14180,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13689,7 +14245,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13750,7 +14310,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13994,7 +14558,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14116,7 +14684,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14177,7 +14749,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14238,7 +14814,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14299,7 +14879,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14421,7 +15005,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14482,7 +15070,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14543,7 +15135,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14726,7 +15322,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14787,7 +15387,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14909,7 +15513,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14970,7 +15578,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15031,7 +15643,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15092,7 +15708,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15218,7 +15838,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15340,7 +15964,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15401,7 +16029,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15462,7 +16094,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15584,7 +16220,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15645,7 +16285,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15950,7 +16594,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16072,7 +16720,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16133,7 +16785,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16194,7 +16850,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16316,7 +16976,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16438,7 +17102,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16560,7 +17228,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16747,7 +17419,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16808,7 +17484,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16869,7 +17549,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16991,7 +17675,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17174,7 +17862,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17235,7 +17927,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17296,7 +17992,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17479,7 +18179,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17601,7 +18305,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17723,7 +18431,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17845,7 +18557,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17906,7 +18622,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18089,7 +18809,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18150,7 +18874,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18211,7 +18939,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18272,7 +19004,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18333,7 +19069,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18394,7 +19134,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18516,7 +19260,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18577,7 +19325,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18638,7 +19390,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18699,7 +19455,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18760,7 +19520,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18821,7 +19585,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19004,7 +19772,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19065,7 +19837,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19187,7 +19963,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19248,7 +20028,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19309,7 +20093,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19370,7 +20158,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19431,7 +20223,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19492,7 +20288,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19553,7 +20353,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19675,7 +20479,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19858,7 +20666,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19919,7 +20731,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20041,7 +20857,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20102,7 +20922,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20285,7 +21109,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20346,7 +21174,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20407,7 +21239,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/may-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/may-2026.xlsx
@@ -2907,7 +2907,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -19427,7 +19427,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
